--- a/data/trans_orig/Q17F_D_R2-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/Q17F_D_R2-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el tiempo de espera en días hasta la consulta en el centro sanitario, en cuartiles (base 2023) en 2007</t>
+          <t>Población según el tiempo de espera en días hasta la consulta en el centro sanitario, en cuartiles (base 2023) en 2007 (tasa de respuesta: 92,28%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>27807</t>
+          <t>28218</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>51394</t>
+          <t>50455</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>17,16%</t>
+          <t>16,85%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>30174</t>
+          <t>30675</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>54246</t>
+          <t>54211</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>64694</t>
+          <t>63918</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>98217</t>
+          <t>98627</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,41%</t>
+          <t>12,46%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10990</t>
+          <t>10524</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>26361</t>
+          <t>26180</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>28049</t>
+          <t>29285</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>52739</t>
+          <t>54121</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>10,99%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>44021</t>
+          <t>43185</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>71964</t>
+          <t>74107</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>9,36%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>23860</t>
+          <t>25116</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>45520</t>
+          <t>47113</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>15,2%</t>
+          <t>15,73%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>33866</t>
+          <t>35747</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>59759</t>
+          <t>61851</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>12,57%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>65186</t>
+          <t>65819</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>98049</t>
+          <t>98851</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>12,38%</t>
+          <t>12,49%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>193663</t>
+          <t>194450</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>225089</t>
+          <t>225400</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>64,67%</t>
+          <t>64,93%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>75,16%</t>
+          <t>75,27%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>344606</t>
+          <t>345237</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>384174</t>
+          <t>384603</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>70,01%</t>
+          <t>70,14%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>78,05%</t>
+          <t>78,13%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>548887</t>
+          <t>551322</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>598475</t>
+          <t>600005</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>69,33%</t>
+          <t>69,64%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>75,59%</t>
+          <t>75,79%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>17496</t>
+          <t>17433</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>35098</t>
+          <t>36239</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>14,85%</t>
+          <t>15,33%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>35882</t>
+          <t>36687</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>62960</t>
+          <t>63093</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>17,16%</t>
+          <t>17,2%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>59527</t>
+          <t>58673</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>92090</t>
+          <t>93754</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>15,27%</t>
+          <t>15,54%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>20653</t>
+          <t>20317</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>42216</t>
+          <t>40997</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>17,86%</t>
+          <t>17,34%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>18851</t>
+          <t>19317</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>39775</t>
+          <t>39620</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>44069</t>
+          <t>44201</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>73286</t>
+          <t>74377</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>12,33%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>11056</t>
+          <t>11438</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>27576</t>
+          <t>27731</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>11,73%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>26020</t>
+          <t>25111</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>48791</t>
+          <t>49165</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>13,4%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>42528</t>
+          <t>40622</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>70793</t>
+          <t>69933</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>11,59%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>148246</t>
+          <t>148926</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>175565</t>
+          <t>176162</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>62,72%</t>
+          <t>63,01%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>74,28%</t>
+          <t>74,53%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>236174</t>
+          <t>236814</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>271534</t>
+          <t>271932</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>64,38%</t>
+          <t>64,55%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>74,01%</t>
+          <t>74,12%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>393635</t>
+          <t>394612</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>439135</t>
+          <t>439704</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>65,25%</t>
+          <t>65,42%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>72,8%</t>
+          <t>72,89%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>5166</t>
+          <t>5351</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>19112</t>
+          <t>19538</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>27,6%</t>
+          <t>28,22%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>8361</t>
+          <t>8123</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>22437</t>
+          <t>21517</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>20,55%</t>
+          <t>19,71%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>15592</t>
+          <t>15614</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>35949</t>
+          <t>35491</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>20,15%</t>
+          <t>19,89%</t>
         </is>
       </c>
     </row>
@@ -1984,12 +1984,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1894</t>
+          <t>1876</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>11294</t>
+          <t>11946</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1999,12 +1999,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>16,31%</t>
+          <t>17,25%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2019,12 +2019,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>4927</t>
+          <t>4527</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>17349</t>
+          <t>17223</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2034,12 +2034,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>15,89%</t>
+          <t>15,78%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2054,12 +2054,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>8651</t>
+          <t>8794</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>23546</t>
+          <t>23062</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2069,12 +2069,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>12,93%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1055</t>
+          <t>967</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10311</t>
+          <t>10354</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>14,89%</t>
+          <t>14,95%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4731</t>
+          <t>4899</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>16615</t>
+          <t>17522</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>15,22%</t>
+          <t>16,05%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>8608</t>
+          <t>7952</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>23291</t>
+          <t>22836</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>13,05%</t>
+          <t>12,8%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>40157</t>
+          <t>40017</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>55908</t>
+          <t>56245</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>58,0%</t>
+          <t>57,8%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>80,75%</t>
+          <t>81,23%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>65395</t>
+          <t>65599</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>84699</t>
+          <t>84322</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>59,9%</t>
+          <t>60,09%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>77,58%</t>
+          <t>77,23%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>112636</t>
+          <t>111743</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>136084</t>
+          <t>136255</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>63,13%</t>
+          <t>62,63%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>76,27%</t>
+          <t>76,37%</t>
         </is>
       </c>
     </row>
@@ -2440,12 +2440,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>59288</t>
+          <t>59039</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>90084</t>
+          <t>90940</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2455,12 +2455,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>14,89%</t>
+          <t>15,03%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,12 +2475,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>85481</t>
+          <t>83660</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>123824</t>
+          <t>124655</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2490,12 +2490,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>12,87%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,12 +2510,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>153636</t>
+          <t>153644</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>203874</t>
+          <t>203563</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2525,12 +2525,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>12,94%</t>
         </is>
       </c>
     </row>
@@ -2553,12 +2553,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>39471</t>
+          <t>39498</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>66480</t>
+          <t>67346</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2568,12 +2568,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,12 +2588,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>61221</t>
+          <t>61900</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>95910</t>
+          <t>96555</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>9,97%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,12 +2623,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>110451</t>
+          <t>109685</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>152006</t>
+          <t>154900</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2638,12 +2638,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>9,85%</t>
         </is>
       </c>
     </row>
@@ -2666,12 +2666,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>44468</t>
+          <t>43740</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>72432</t>
+          <t>72200</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2681,12 +2681,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>11,97%</t>
+          <t>11,93%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2701,12 +2701,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>76114</t>
+          <t>74880</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>110558</t>
+          <t>111501</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2716,12 +2716,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>11,52%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2736,12 +2736,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>126854</t>
+          <t>126833</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>173179</t>
+          <t>170733</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2756,7 +2756,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>10,85%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>400562</t>
+          <t>397595</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>444042</t>
+          <t>444250</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>66,2%</t>
+          <t>65,71%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>73,39%</t>
+          <t>73,42%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>665630</t>
+          <t>664931</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>722273</t>
+          <t>722375</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>68,74%</t>
+          <t>68,67%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>74,59%</t>
+          <t>74,6%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1080683</t>
+          <t>1077471</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1151721</t>
+          <t>1150654</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>68,69%</t>
+          <t>68,48%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>73,2%</t>
+          <t>73,13%</t>
         </is>
       </c>
     </row>
@@ -3045,7 +3045,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el tiempo de espera en días hasta la consulta en el centro sanitario, en cuartiles (base 2023) en 2012</t>
+          <t>Población según el tiempo de espera en días hasta la consulta en el centro sanitario, en cuartiles (base 2023) en 2012 (tasa de respuesta: 95,76%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3240,12 +3240,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>32192</t>
+          <t>32513</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>57983</t>
+          <t>57999</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3255,7 +3255,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -3275,12 +3275,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>32610</t>
+          <t>31821</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>58838</t>
+          <t>57796</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3290,12 +3290,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>10,96%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3310,12 +3310,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>69903</t>
+          <t>70240</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>105277</t>
+          <t>106393</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3325,12 +3325,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>12,45%</t>
         </is>
       </c>
     </row>
@@ -3353,12 +3353,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>13184</t>
+          <t>14415</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>31456</t>
+          <t>32090</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3368,12 +3368,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3388,12 +3388,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>28098</t>
+          <t>27753</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>53259</t>
+          <t>52010</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3423,12 +3423,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>47135</t>
+          <t>46892</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>79971</t>
+          <t>77755</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>9,1%</t>
         </is>
       </c>
     </row>
@@ -3466,12 +3466,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>22524</t>
+          <t>21913</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>47450</t>
+          <t>45372</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>13,87%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3501,12 +3501,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>43493</t>
+          <t>43444</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>71641</t>
+          <t>70982</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>13,46%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3536,12 +3536,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>70714</t>
+          <t>71343</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>108346</t>
+          <t>109024</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>12,76%</t>
         </is>
       </c>
     </row>
@@ -3579,12 +3579,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>209349</t>
+          <t>209640</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>243647</t>
+          <t>245878</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3594,12 +3594,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>64,01%</t>
+          <t>64,09%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>74,49%</t>
+          <t>75,17%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3614,12 +3614,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>366984</t>
+          <t>368631</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>406968</t>
+          <t>408301</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3629,12 +3629,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>69,58%</t>
+          <t>69,9%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>77,16%</t>
+          <t>77,42%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3649,12 +3649,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>587161</t>
+          <t>588751</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>644387</t>
+          <t>643826</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3664,12 +3664,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>68,72%</t>
+          <t>68,9%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>75,41%</t>
+          <t>75,35%</t>
         </is>
       </c>
     </row>
@@ -3809,12 +3809,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>26631</t>
+          <t>27081</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>50107</t>
+          <t>49897</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3824,12 +3824,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>14,61%</t>
+          <t>14,54%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3844,12 +3844,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>47522</t>
+          <t>48175</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>77694</t>
+          <t>75977</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>16,36%</t>
+          <t>16,0%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3879,12 +3879,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>81831</t>
+          <t>80843</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>118543</t>
+          <t>118601</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>14,49%</t>
+          <t>14,5%</t>
         </is>
       </c>
     </row>
@@ -3922,12 +3922,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9934</t>
+          <t>10268</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>28533</t>
+          <t>27410</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3937,12 +3937,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3957,12 +3957,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>34157</t>
+          <t>35964</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>61795</t>
+          <t>63568</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3972,12 +3972,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>13,39%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3992,12 +3992,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>50172</t>
+          <t>49739</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>82337</t>
+          <t>82453</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4007,12 +4007,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>10,08%</t>
         </is>
       </c>
     </row>
@@ -4035,12 +4035,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>27285</t>
+          <t>27462</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>51367</t>
+          <t>51405</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4050,12 +4050,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>14,97%</t>
+          <t>14,98%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>51546</t>
+          <t>51500</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>82193</t>
+          <t>84420</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4085,12 +4085,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>17,31%</t>
+          <t>17,78%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>86635</t>
+          <t>84311</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>125305</t>
+          <t>124043</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4120,12 +4120,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>10,31%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>15,32%</t>
+          <t>15,16%</t>
         </is>
       </c>
     </row>
@@ -4148,12 +4148,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>231050</t>
+          <t>233639</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>266639</t>
+          <t>265804</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4163,12 +4163,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>67,35%</t>
+          <t>68,1%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>77,72%</t>
+          <t>77,48%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>278127</t>
+          <t>276152</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>320812</t>
+          <t>320913</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4198,12 +4198,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>58,57%</t>
+          <t>58,15%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>67,56%</t>
+          <t>67,58%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>520851</t>
+          <t>519502</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>576641</t>
+          <t>576897</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4233,12 +4233,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>63,68%</t>
+          <t>63,51%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>70,5%</t>
+          <t>70,53%</t>
         </is>
       </c>
     </row>
@@ -4378,12 +4378,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>6580</t>
+          <t>6505</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>22035</t>
+          <t>21511</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4393,12 +4393,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>29,46%</t>
+          <t>28,76%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>6122</t>
+          <t>6310</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>19999</t>
+          <t>19093</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4428,12 +4428,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>19,09%</t>
+          <t>18,23%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>14585</t>
+          <t>15199</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>34036</t>
+          <t>35806</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4463,12 +4463,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>18,96%</t>
+          <t>19,94%</t>
         </is>
       </c>
     </row>
@@ -4491,12 +4491,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>894</t>
+          <t>902</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>7780</t>
+          <t>8036</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>10,74%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>4339</t>
+          <t>4488</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>17501</t>
+          <t>17906</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4541,12 +4541,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>16,71%</t>
+          <t>17,09%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>6272</t>
+          <t>6571</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>22162</t>
+          <t>21488</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -4576,12 +4576,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>11,97%</t>
         </is>
       </c>
     </row>
@@ -4604,12 +4604,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>1963</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>12884</t>
+          <t>14547</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4619,12 +4619,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>17,23%</t>
+          <t>19,45%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4639,12 +4639,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3880</t>
+          <t>4002</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>15331</t>
+          <t>16159</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4654,12 +4654,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>14,63%</t>
+          <t>15,42%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4674,12 +4674,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>7523</t>
+          <t>7273</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>23001</t>
+          <t>22898</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4689,12 +4689,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>12,75%</t>
         </is>
       </c>
     </row>
@@ -4717,12 +4717,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>43981</t>
+          <t>43472</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>61098</t>
+          <t>61479</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4732,12 +4732,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>58,8%</t>
+          <t>58,12%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>81,68%</t>
+          <t>82,19%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4752,12 +4752,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>64642</t>
+          <t>65271</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>84232</t>
+          <t>84982</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4767,12 +4767,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>61,71%</t>
+          <t>62,3%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>80,41%</t>
+          <t>81,12%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4787,12 +4787,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>117100</t>
+          <t>113758</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>143033</t>
+          <t>140688</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4802,12 +4802,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>65,22%</t>
+          <t>63,35%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>79,66%</t>
+          <t>78,35%</t>
         </is>
       </c>
     </row>
@@ -4947,12 +4947,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>75724</t>
+          <t>75129</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>112754</t>
+          <t>112036</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -4962,12 +4962,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>10,09%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>15,14%</t>
+          <t>15,04%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -4982,12 +4982,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>96227</t>
+          <t>96483</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>138335</t>
+          <t>138917</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -4997,12 +4997,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>8,72%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>12,55%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5017,12 +5017,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>182085</t>
+          <t>182171</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>237221</t>
+          <t>238829</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5032,12 +5032,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>12,9%</t>
         </is>
       </c>
     </row>
@@ -5060,12 +5060,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>30101</t>
+          <t>30684</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>56664</t>
+          <t>57485</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5075,12 +5075,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5095,12 +5095,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>76606</t>
+          <t>77325</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>117162</t>
+          <t>116455</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5110,12 +5110,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>10,52%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5130,12 +5130,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>115888</t>
+          <t>116479</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>162519</t>
+          <t>163003</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>8,8%</t>
         </is>
       </c>
     </row>
@@ -5173,12 +5173,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>59756</t>
+          <t>60400</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>97425</t>
+          <t>97174</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>13,04%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5208,12 +5208,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>109912</t>
+          <t>111277</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>152897</t>
+          <t>155406</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5223,12 +5223,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>14,04%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5243,12 +5243,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>181790</t>
+          <t>180926</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>238954</t>
+          <t>236973</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5258,12 +5258,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>12,8%</t>
         </is>
       </c>
     </row>
@@ -5286,12 +5286,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>507524</t>
+          <t>505037</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>558539</t>
+          <t>554754</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5301,12 +5301,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>68,13%</t>
+          <t>67,79%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>74,98%</t>
+          <t>74,47%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5321,12 +5321,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>734282</t>
+          <t>725810</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>799969</t>
+          <t>790775</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5336,12 +5336,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>66,33%</t>
+          <t>65,56%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>72,26%</t>
+          <t>71,43%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5356,12 +5356,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1257282</t>
+          <t>1255101</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1334988</t>
+          <t>1335009</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5371,7 +5371,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>67,89%</t>
+          <t>67,77%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -5552,7 +5552,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el tiempo de espera en días hasta la consulta en el centro sanitario, en cuartiles (base 2023) en 2016</t>
+          <t>Población según el tiempo de espera en días hasta la consulta en el centro sanitario, en cuartiles (base 2023) en 2016 (tasa de respuesta: 95,3%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5747,12 +5747,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>21020</t>
+          <t>21829</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>41519</t>
+          <t>41942</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5762,47 +5762,47 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
+          <t>8,84%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>16,99%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>45643</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>34300</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>61378</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>11,32%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
           <t>8,51%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>16,81%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>45643</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>33322</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>59694</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>11,32%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>8,26%</t>
-        </is>
-      </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>14,8%</t>
+          <t>15,22%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5817,12 +5817,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>58292</t>
+          <t>59220</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>94681</t>
+          <t>94391</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5832,12 +5832,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>14,56%</t>
+          <t>14,52%</t>
         </is>
       </c>
     </row>
@@ -5860,12 +5860,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7734</t>
+          <t>7354</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>22237</t>
+          <t>22454</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5875,12 +5875,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5895,12 +5895,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>20123</t>
+          <t>20713</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>42157</t>
+          <t>43573</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5910,12 +5910,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>10,81%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5930,12 +5930,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>32677</t>
+          <t>32252</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>58893</t>
+          <t>59765</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5945,12 +5945,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>9,19%</t>
         </is>
       </c>
     </row>
@@ -5973,12 +5973,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>17615</t>
+          <t>17712</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>37410</t>
+          <t>37165</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>15,05%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6008,12 +6008,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>26395</t>
+          <t>26009</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>50482</t>
+          <t>49935</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6023,12 +6023,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>12,38%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>48235</t>
+          <t>50296</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>79841</t>
+          <t>79798</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6058,12 +6058,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>12,27%</t>
         </is>
       </c>
     </row>
@@ -6086,12 +6086,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>162024</t>
+          <t>161321</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>190908</t>
+          <t>189252</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6101,12 +6101,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>65,62%</t>
+          <t>65,33%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>77,31%</t>
+          <t>76,64%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6121,12 +6121,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>270651</t>
+          <t>270132</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>307380</t>
+          <t>308411</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6136,12 +6136,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>67,12%</t>
+          <t>66,99%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>76,23%</t>
+          <t>76,48%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6156,12 +6156,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>442046</t>
+          <t>444652</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>489447</t>
+          <t>489817</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6171,12 +6171,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>67,99%</t>
+          <t>68,39%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>75,28%</t>
+          <t>75,34%</t>
         </is>
       </c>
     </row>
@@ -6316,12 +6316,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>31852</t>
+          <t>31598</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>57936</t>
+          <t>58830</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6331,12 +6331,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>13,09%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6351,12 +6351,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>60664</t>
+          <t>60955</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>94359</t>
+          <t>95186</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6366,12 +6366,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>16,69%</t>
+          <t>16,84%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6386,12 +6386,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>100446</t>
+          <t>100246</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>144239</t>
+          <t>141868</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6401,12 +6401,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>14,22%</t>
+          <t>13,98%</t>
         </is>
       </c>
     </row>
@@ -6429,12 +6429,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>15808</t>
+          <t>16162</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>36603</t>
+          <t>36862</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6444,12 +6444,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>46886</t>
+          <t>47840</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>78088</t>
+          <t>76884</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6479,12 +6479,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6499,12 +6499,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>68743</t>
+          <t>69073</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>104465</t>
+          <t>107366</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6514,12 +6514,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>10,58%</t>
         </is>
       </c>
     </row>
@@ -6542,12 +6542,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>43937</t>
+          <t>42768</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>72567</t>
+          <t>71756</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6557,12 +6557,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>16,15%</t>
+          <t>15,97%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>56635</t>
+          <t>56676</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>89113</t>
+          <t>90127</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6592,12 +6592,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>10,03%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>15,94%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6612,12 +6612,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>106469</t>
+          <t>107118</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>152027</t>
+          <t>150758</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6627,12 +6627,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>14,98%</t>
+          <t>14,86%</t>
         </is>
       </c>
     </row>
@@ -6655,12 +6655,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>304459</t>
+          <t>305219</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>344360</t>
+          <t>344723</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6670,12 +6670,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>67,76%</t>
+          <t>67,93%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>76,64%</t>
+          <t>76,72%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6690,12 +6690,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>330963</t>
+          <t>330609</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>378062</t>
+          <t>377784</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6705,12 +6705,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>58,55%</t>
+          <t>58,48%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>66,88%</t>
+          <t>66,83%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6725,12 +6725,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>649224</t>
+          <t>650700</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>713124</t>
+          <t>711402</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6740,12 +6740,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>63,99%</t>
+          <t>64,13%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>70,28%</t>
+          <t>70,11%</t>
         </is>
       </c>
     </row>
@@ -6885,12 +6885,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>7499</t>
+          <t>7560</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>23481</t>
+          <t>23411</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6900,12 +6900,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>20,47%</t>
+          <t>20,4%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6920,12 +6920,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>9522</t>
+          <t>9386</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>26178</t>
+          <t>26258</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6935,12 +6935,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>19,87%</t>
+          <t>19,93%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6955,12 +6955,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>20455</t>
+          <t>20357</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>43851</t>
+          <t>42315</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6970,12 +6970,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>17,79%</t>
+          <t>17,17%</t>
         </is>
       </c>
     </row>
@@ -6998,12 +6998,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5756</t>
+          <t>5502</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>19903</t>
+          <t>19065</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7013,12 +7013,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>17,35%</t>
+          <t>16,62%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -7033,12 +7033,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>8680</t>
+          <t>8737</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>24118</t>
+          <t>23150</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7048,12 +7048,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>18,31%</t>
+          <t>17,57%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -7068,12 +7068,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>17289</t>
+          <t>17445</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>37475</t>
+          <t>37270</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7083,12 +7083,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>15,21%</t>
+          <t>15,12%</t>
         </is>
       </c>
     </row>
@@ -7111,12 +7111,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>13584</t>
+          <t>13725</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>31289</t>
+          <t>31297</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7126,12 +7126,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>11,96%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>27,27%</t>
+          <t>27,28%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7146,12 +7146,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>7643</t>
+          <t>8541</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>21765</t>
+          <t>22950</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7161,12 +7161,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>17,42%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7181,12 +7181,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>25642</t>
+          <t>25851</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>48738</t>
+          <t>50076</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7196,12 +7196,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>19,77%</t>
+          <t>20,32%</t>
         </is>
       </c>
     </row>
@@ -7224,12 +7224,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>57209</t>
+          <t>56988</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>79466</t>
+          <t>78727</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7239,12 +7239,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>49,86%</t>
+          <t>49,67%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>69,26%</t>
+          <t>68,61%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7259,12 +7259,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>74350</t>
+          <t>73938</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>96767</t>
+          <t>96438</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7274,12 +7274,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>56,44%</t>
+          <t>56,13%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>73,46%</t>
+          <t>73,21%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7294,12 +7294,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>137250</t>
+          <t>139237</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>169522</t>
+          <t>170321</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7309,12 +7309,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>55,69%</t>
+          <t>56,49%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>68,78%</t>
+          <t>69,11%</t>
         </is>
       </c>
     </row>
@@ -7454,12 +7454,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>68982</t>
+          <t>72712</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>105671</t>
+          <t>109975</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7469,12 +7469,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>13,03%</t>
+          <t>13,56%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7489,12 +7489,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>115919</t>
+          <t>116166</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>162795</t>
+          <t>160977</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7504,12 +7504,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10,54%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>14,8%</t>
+          <t>14,63%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7524,12 +7524,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>198685</t>
+          <t>198345</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>258719</t>
+          <t>256271</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7539,12 +7539,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>13,41%</t>
         </is>
       </c>
     </row>
@@ -7567,12 +7567,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>36210</t>
+          <t>35974</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>64360</t>
+          <t>64443</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7582,12 +7582,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7602,12 +7602,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>87609</t>
+          <t>87995</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>127170</t>
+          <t>128761</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7617,12 +7617,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>11,7%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7637,12 +7637,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>132284</t>
+          <t>130262</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>181031</t>
+          <t>182400</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7652,12 +7652,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>9,54%</t>
         </is>
       </c>
     </row>
@@ -7680,12 +7680,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>86321</t>
+          <t>86452</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>124165</t>
+          <t>126648</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7695,12 +7695,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>10,66%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>15,62%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7715,12 +7715,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>101831</t>
+          <t>102421</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>146737</t>
+          <t>145921</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7730,12 +7730,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>13,26%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7750,12 +7750,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>199553</t>
+          <t>198252</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>256487</t>
+          <t>259132</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7765,12 +7765,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>13,56%</t>
         </is>
       </c>
     </row>
@@ -7793,12 +7793,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>541157</t>
+          <t>541649</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>593830</t>
+          <t>593956</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7808,12 +7808,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>66,73%</t>
+          <t>66,79%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>73,22%</t>
+          <t>73,24%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7828,12 +7828,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>701947</t>
+          <t>697678</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>764314</t>
+          <t>761883</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7843,12 +7843,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>63,8%</t>
+          <t>63,41%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>69,47%</t>
+          <t>69,24%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7863,12 +7863,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1258531</t>
+          <t>1258184</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1344063</t>
+          <t>1343151</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7878,12 +7878,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>65,85%</t>
+          <t>65,83%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>70,32%</t>
+          <t>70,27%</t>
         </is>
       </c>
     </row>
@@ -8059,7 +8059,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el tiempo de espera en días hasta la consulta en el centro sanitario, en cuartiles (base 2023) en 2023</t>
+          <t>Población según el tiempo de espera en días hasta la consulta en el centro sanitario, en cuartiles (base 2023) en 2023 (tasa de respuesta: 94,38%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8254,12 +8254,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>15976</t>
+          <t>15650</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>30620</t>
+          <t>31106</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8269,12 +8269,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>12,13%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>23,74%</t>
+          <t>24,11%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8289,12 +8289,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>34613</t>
+          <t>33795</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>53049</t>
+          <t>52602</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8304,12 +8304,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>15,41%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>24,19%</t>
+          <t>23,99%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8324,12 +8324,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>54641</t>
+          <t>53744</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>77224</t>
+          <t>77995</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8339,12 +8339,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>15,43%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>22,17%</t>
+          <t>22,4%</t>
         </is>
       </c>
     </row>
@@ -8367,12 +8367,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>32621</t>
+          <t>32535</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>52230</t>
+          <t>52797</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8382,12 +8382,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>25,29%</t>
+          <t>25,22%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>40,49%</t>
+          <t>40,93%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8402,12 +8402,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>53756</t>
+          <t>54658</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>79241</t>
+          <t>80000</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8417,12 +8417,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>24,52%</t>
+          <t>24,93%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>36,14%</t>
+          <t>36,48%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8437,12 +8437,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>93892</t>
+          <t>93425</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>125754</t>
+          <t>123457</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8452,12 +8452,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>26,96%</t>
+          <t>26,83%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>36,11%</t>
+          <t>35,45%</t>
         </is>
       </c>
     </row>
@@ -8480,12 +8480,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>15969</t>
+          <t>16251</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>31348</t>
+          <t>31595</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8495,12 +8495,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>12,38%</t>
+          <t>12,6%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>24,3%</t>
+          <t>24,49%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8515,12 +8515,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>37941</t>
+          <t>37040</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>55366</t>
+          <t>55333</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8530,12 +8530,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>17,3%</t>
+          <t>16,89%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>25,25%</t>
+          <t>25,23%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8550,12 +8550,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>58607</t>
+          <t>57745</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>82007</t>
+          <t>81840</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8565,12 +8565,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>16,58%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>23,55%</t>
+          <t>23,5%</t>
         </is>
       </c>
     </row>
@@ -8593,12 +8593,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>33676</t>
+          <t>32857</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>52330</t>
+          <t>51192</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8608,12 +8608,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>26,11%</t>
+          <t>25,47%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>40,57%</t>
+          <t>39,68%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8628,12 +8628,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>54440</t>
+          <t>54278</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>75910</t>
+          <t>75301</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>24,83%</t>
+          <t>24,75%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>34,62%</t>
+          <t>34,34%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8663,12 +8663,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>92441</t>
+          <t>93480</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>120512</t>
+          <t>122026</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8678,12 +8678,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>26,54%</t>
+          <t>26,84%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>34,6%</t>
+          <t>35,04%</t>
         </is>
       </c>
     </row>
@@ -8823,12 +8823,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>46752</t>
+          <t>45438</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>73012</t>
+          <t>72811</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8838,12 +8838,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>13,26%</t>
+          <t>12,89%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>20,7%</t>
+          <t>20,65%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8858,12 +8858,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>54436</t>
+          <t>53971</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>109464</t>
+          <t>112293</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8873,12 +8873,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>22,7%</t>
+          <t>23,29%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8893,12 +8893,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>113015</t>
+          <t>109826</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>175346</t>
+          <t>172104</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8908,12 +8908,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>13,15%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>21,0%</t>
+          <t>20,61%</t>
         </is>
       </c>
     </row>
@@ -8936,12 +8936,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>83329</t>
+          <t>80823</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>118758</t>
+          <t>115090</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8951,12 +8951,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>23,63%</t>
+          <t>22,92%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>33,68%</t>
+          <t>32,64%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8971,12 +8971,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>84116</t>
+          <t>77916</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>156368</t>
+          <t>156805</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8986,12 +8986,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>17,44%</t>
+          <t>16,16%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>32,42%</t>
+          <t>32,51%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9006,12 +9006,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>165411</t>
+          <t>175433</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>257151</t>
+          <t>258929</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9021,12 +9021,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>19,81%</t>
+          <t>21,01%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>30,8%</t>
+          <t>31,01%</t>
         </is>
       </c>
     </row>
@@ -9049,12 +9049,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>51631</t>
+          <t>51885</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>86203</t>
+          <t>84517</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9064,12 +9064,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>14,64%</t>
+          <t>14,71%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>24,45%</t>
+          <t>23,97%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9084,12 +9084,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>69888</t>
+          <t>70726</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>251124</t>
+          <t>263283</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9099,12 +9099,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>14,49%</t>
+          <t>14,67%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>52,07%</t>
+          <t>54,59%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9119,12 +9119,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>135581</t>
+          <t>134286</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>371417</t>
+          <t>341891</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9134,12 +9134,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>16,08%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>44,49%</t>
+          <t>40,95%</t>
         </is>
       </c>
     </row>
@@ -9162,12 +9162,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>107651</t>
+          <t>110776</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>149132</t>
+          <t>151817</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>30,53%</t>
+          <t>31,41%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>42,29%</t>
+          <t>43,05%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -9197,12 +9197,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>84860</t>
+          <t>84361</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>160916</t>
+          <t>160297</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9212,12 +9212,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>17,49%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>33,37%</t>
+          <t>33,24%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -9232,12 +9232,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>194500</t>
+          <t>192310</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>296971</t>
+          <t>296594</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9247,12 +9247,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>23,3%</t>
+          <t>23,03%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>35,57%</t>
+          <t>35,53%</t>
         </is>
       </c>
     </row>
@@ -9392,12 +9392,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>20662</t>
+          <t>20610</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>40781</t>
+          <t>39757</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9407,12 +9407,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>16,66%</t>
+          <t>16,62%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>32,88%</t>
+          <t>32,05%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9427,12 +9427,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>17037</t>
+          <t>17184</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>31171</t>
+          <t>32092</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9442,12 +9442,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>11,62%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>21,07%</t>
+          <t>21,7%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9462,12 +9462,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>42204</t>
+          <t>40794</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>66295</t>
+          <t>66635</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9477,12 +9477,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>15,52%</t>
+          <t>15,0%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>24,38%</t>
+          <t>24,5%</t>
         </is>
       </c>
     </row>
@@ -9505,12 +9505,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>24620</t>
+          <t>24410</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>44446</t>
+          <t>44178</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -9520,12 +9520,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>19,85%</t>
+          <t>19,68%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>35,83%</t>
+          <t>35,61%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -9540,12 +9540,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>38328</t>
+          <t>38814</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>59122</t>
+          <t>57575</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9555,12 +9555,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>25,91%</t>
+          <t>26,24%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>39,97%</t>
+          <t>38,92%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -9575,12 +9575,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>68467</t>
+          <t>69294</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>97285</t>
+          <t>98532</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -9590,12 +9590,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>25,18%</t>
+          <t>25,48%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>35,77%</t>
+          <t>36,23%</t>
         </is>
       </c>
     </row>
@@ -9618,12 +9618,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>13348</t>
+          <t>14066</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>31735</t>
+          <t>32616</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9633,12 +9633,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>11,34%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>25,58%</t>
+          <t>26,29%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9653,12 +9653,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>16092</t>
+          <t>16024</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>33043</t>
+          <t>31728</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9668,12 +9668,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>10,83%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>22,34%</t>
+          <t>21,45%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9688,12 +9688,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>33095</t>
+          <t>32496</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>57136</t>
+          <t>55906</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9703,12 +9703,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>11,95%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>21,01%</t>
+          <t>20,56%</t>
         </is>
       </c>
     </row>
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>29692</t>
+          <t>29655</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>51302</t>
+          <t>51854</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9746,12 +9746,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>23,94%</t>
+          <t>23,91%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>41,36%</t>
+          <t>41,8%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9766,12 +9766,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>43797</t>
+          <t>43664</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>63118</t>
+          <t>64370</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9781,12 +9781,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>29,61%</t>
+          <t>29,52%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>42,67%</t>
+          <t>43,52%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9801,12 +9801,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>79223</t>
+          <t>78279</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>109859</t>
+          <t>108881</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9816,12 +9816,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>29,13%</t>
+          <t>28,78%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>40,4%</t>
+          <t>40,04%</t>
         </is>
       </c>
     </row>
@@ -9961,12 +9961,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>92069</t>
+          <t>90994</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>130341</t>
+          <t>130505</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9976,12 +9976,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>15,2%</t>
+          <t>15,02%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>21,52%</t>
+          <t>21,55%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9996,12 +9996,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>116931</t>
+          <t>116052</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>182598</t>
+          <t>180560</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10011,12 +10011,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13,77%</t>
+          <t>13,66%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>21,5%</t>
+          <t>21,26%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10031,12 +10031,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>223360</t>
+          <t>225253</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>296625</t>
+          <t>298623</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10046,12 +10046,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>15,35%</t>
+          <t>15,48%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>20,38%</t>
+          <t>20,52%</t>
         </is>
       </c>
     </row>
@@ -10074,12 +10074,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>154127</t>
+          <t>153240</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>196565</t>
+          <t>196919</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10089,12 +10089,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>25,45%</t>
+          <t>25,3%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>32,45%</t>
+          <t>32,51%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10109,12 +10109,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>176204</t>
+          <t>176315</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>273028</t>
+          <t>273411</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10124,12 +10124,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>20,74%</t>
+          <t>20,76%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>32,14%</t>
+          <t>32,19%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10144,12 +10144,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>346228</t>
+          <t>355743</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>453611</t>
+          <t>455221</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10159,12 +10159,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>23,79%</t>
+          <t>24,45%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>31,17%</t>
+          <t>31,28%</t>
         </is>
       </c>
     </row>
@@ -10187,12 +10187,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>90653</t>
+          <t>93618</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>131885</t>
+          <t>132532</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10202,12 +10202,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>14,97%</t>
+          <t>15,46%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>21,78%</t>
+          <t>21,88%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -10222,12 +10222,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>138858</t>
+          <t>139544</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>383042</t>
+          <t>395670</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10237,12 +10237,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>16,35%</t>
+          <t>16,43%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>45,09%</t>
+          <t>46,58%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -10257,12 +10257,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>244594</t>
+          <t>245280</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>548583</t>
+          <t>494161</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>16,81%</t>
+          <t>16,86%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>37,7%</t>
+          <t>33,96%</t>
         </is>
       </c>
     </row>
@@ -10300,12 +10300,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>185702</t>
+          <t>186270</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>238440</t>
+          <t>235411</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10315,12 +10315,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>30,66%</t>
+          <t>30,75%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>39,37%</t>
+          <t>38,87%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10335,12 +10335,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>183142</t>
+          <t>178253</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>281476</t>
+          <t>280993</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10350,12 +10350,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>21,56%</t>
+          <t>20,98%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>33,14%</t>
+          <t>33,08%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10370,12 +10370,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>379998</t>
+          <t>387525</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>502623</t>
+          <t>500011</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10385,12 +10385,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>26,11%</t>
+          <t>26,63%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>34,54%</t>
+          <t>34,36%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Q17F_D_R2-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/Q17F_D_R2-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>28218</t>
+          <t>28692</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>50455</t>
+          <t>49707</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>16,85%</t>
+          <t>16,6%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>30675</t>
+          <t>30309</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>54211</t>
+          <t>53645</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>10,9%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>63918</t>
+          <t>64571</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>98627</t>
+          <t>98339</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>12,42%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10524</t>
+          <t>10467</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>26180</t>
+          <t>26139</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>29285</t>
+          <t>29005</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>54121</t>
+          <t>54268</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>11,02%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>43185</t>
+          <t>44859</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>74107</t>
+          <t>73067</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>9,23%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>25116</t>
+          <t>23930</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>47113</t>
+          <t>45688</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>15,73%</t>
+          <t>15,26%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>35747</t>
+          <t>34964</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>61851</t>
+          <t>59402</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>12,57%</t>
+          <t>12,07%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>65819</t>
+          <t>64977</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>98851</t>
+          <t>98430</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>12,43%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>194450</t>
+          <t>194926</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>225400</t>
+          <t>224068</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>64,93%</t>
+          <t>65,09%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>75,27%</t>
+          <t>74,82%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>345237</t>
+          <t>345504</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>384603</t>
+          <t>381797</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>70,14%</t>
+          <t>70,19%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>78,13%</t>
+          <t>77,56%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>551322</t>
+          <t>549526</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>600005</t>
+          <t>598641</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>69,64%</t>
+          <t>69,41%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>75,79%</t>
+          <t>75,61%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>17433</t>
+          <t>17562</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>36239</t>
+          <t>36680</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>15,52%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>36687</t>
+          <t>35945</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>63093</t>
+          <t>64264</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>17,52%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>58673</t>
+          <t>59482</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>93754</t>
+          <t>92343</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>15,54%</t>
+          <t>15,31%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>20317</t>
+          <t>20497</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>40997</t>
+          <t>41270</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>17,34%</t>
+          <t>17,46%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>19317</t>
+          <t>19355</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>39620</t>
+          <t>40181</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>10,95%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>44201</t>
+          <t>44639</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>74377</t>
+          <t>75442</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>12,51%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>11438</t>
+          <t>11024</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>27731</t>
+          <t>27998</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>11,73%</t>
+          <t>11,84%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>25111</t>
+          <t>25782</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>49165</t>
+          <t>48141</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>13,4%</t>
+          <t>13,12%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>40622</t>
+          <t>42038</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>69933</t>
+          <t>69843</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>11,58%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>148926</t>
+          <t>147216</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>176162</t>
+          <t>176743</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>63,01%</t>
+          <t>62,28%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>74,53%</t>
+          <t>74,77%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>236814</t>
+          <t>234508</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>271932</t>
+          <t>271249</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>64,55%</t>
+          <t>63,92%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>74,12%</t>
+          <t>73,94%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>394612</t>
+          <t>394421</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>439704</t>
+          <t>438533</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>65,42%</t>
+          <t>65,38%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>72,89%</t>
+          <t>72,7%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>5351</t>
+          <t>5016</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>19538</t>
+          <t>19398</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>28,22%</t>
+          <t>28,02%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>8123</t>
+          <t>7610</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>21517</t>
+          <t>22321</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>19,71%</t>
+          <t>20,44%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>15614</t>
+          <t>15186</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>35491</t>
+          <t>34900</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>19,89%</t>
+          <t>19,56%</t>
         </is>
       </c>
     </row>
@@ -1984,12 +1984,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1876</t>
+          <t>1996</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>11946</t>
+          <t>10871</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1999,12 +1999,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>17,25%</t>
+          <t>15,7%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2019,12 +2019,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>4527</t>
+          <t>4717</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>17223</t>
+          <t>16587</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2034,12 +2034,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>15,19%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2054,12 +2054,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>8794</t>
+          <t>8527</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>23062</t>
+          <t>23169</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2069,12 +2069,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>12,93%</t>
+          <t>12,99%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>967</t>
+          <t>1295</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10354</t>
+          <t>10915</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>14,95%</t>
+          <t>15,76%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4899</t>
+          <t>4512</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>17522</t>
+          <t>16885</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>16,05%</t>
+          <t>15,47%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>7952</t>
+          <t>8088</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>22836</t>
+          <t>22729</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,8%</t>
+          <t>12,74%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>40017</t>
+          <t>40388</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>56245</t>
+          <t>56101</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>57,8%</t>
+          <t>58,33%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>81,23%</t>
+          <t>81,02%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>65599</t>
+          <t>66616</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>84322</t>
+          <t>85623</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>60,09%</t>
+          <t>61,02%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>77,23%</t>
+          <t>78,43%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>111743</t>
+          <t>111257</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>136255</t>
+          <t>137266</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>62,63%</t>
+          <t>62,36%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>76,37%</t>
+          <t>76,94%</t>
         </is>
       </c>
     </row>
@@ -2440,12 +2440,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>59039</t>
+          <t>58656</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>90940</t>
+          <t>91638</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2455,12 +2455,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>15,03%</t>
+          <t>15,14%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,12 +2475,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>83660</t>
+          <t>84711</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>124655</t>
+          <t>124464</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2490,12 +2490,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>12,85%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,12 +2510,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>153644</t>
+          <t>155508</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>203563</t>
+          <t>205889</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2525,12 +2525,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>13,09%</t>
         </is>
       </c>
     </row>
@@ -2553,12 +2553,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>39498</t>
+          <t>38939</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>67346</t>
+          <t>67726</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2568,12 +2568,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,12 +2588,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>61900</t>
+          <t>62156</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>96555</t>
+          <t>95795</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,12 +2623,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>109685</t>
+          <t>107163</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>154900</t>
+          <t>149683</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2638,12 +2638,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>9,51%</t>
         </is>
       </c>
     </row>
@@ -2666,12 +2666,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>43740</t>
+          <t>43071</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>72200</t>
+          <t>71848</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2681,12 +2681,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>11,93%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2701,12 +2701,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>74880</t>
+          <t>75987</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>111501</t>
+          <t>112158</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2716,12 +2716,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2736,12 +2736,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>126833</t>
+          <t>126798</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>170733</t>
+          <t>172058</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2756,7 +2756,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>10,94%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>397595</t>
+          <t>399638</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>444250</t>
+          <t>445428</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>65,71%</t>
+          <t>66,05%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>73,42%</t>
+          <t>73,61%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>664931</t>
+          <t>664215</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>722375</t>
+          <t>721034</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>68,67%</t>
+          <t>68,6%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>74,6%</t>
+          <t>74,47%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1077471</t>
+          <t>1080960</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1150654</t>
+          <t>1151152</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>68,48%</t>
+          <t>68,7%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>73,13%</t>
+          <t>73,16%</t>
         </is>
       </c>
     </row>
@@ -3240,12 +3240,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>32513</t>
+          <t>32313</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>57999</t>
+          <t>58696</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3255,12 +3255,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>17,73%</t>
+          <t>17,95%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3275,12 +3275,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>31821</t>
+          <t>31776</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>57796</t>
+          <t>58297</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3290,12 +3290,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>11,05%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3310,12 +3310,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>70240</t>
+          <t>70783</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>106393</t>
+          <t>108962</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3325,12 +3325,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>12,75%</t>
         </is>
       </c>
     </row>
@@ -3353,12 +3353,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>14415</t>
+          <t>14035</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>32090</t>
+          <t>33172</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3368,12 +3368,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3388,12 +3388,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>27753</t>
+          <t>27554</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>52010</t>
+          <t>51446</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3423,12 +3423,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>46892</t>
+          <t>46679</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>77755</t>
+          <t>76573</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>8,96%</t>
         </is>
       </c>
     </row>
@@ -3466,12 +3466,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>21913</t>
+          <t>22497</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>45372</t>
+          <t>47553</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>13,87%</t>
+          <t>14,54%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3501,12 +3501,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>43444</t>
+          <t>43832</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>70982</t>
+          <t>72379</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>13,72%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3536,12 +3536,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>71343</t>
+          <t>70631</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>109024</t>
+          <t>108155</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>12,66%</t>
         </is>
       </c>
     </row>
@@ -3579,12 +3579,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>209640</t>
+          <t>208574</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>245878</t>
+          <t>245191</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3594,12 +3594,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>64,09%</t>
+          <t>63,77%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>75,17%</t>
+          <t>74,96%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3614,12 +3614,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>368631</t>
+          <t>368807</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>408301</t>
+          <t>409252</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3629,12 +3629,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>69,9%</t>
+          <t>69,93%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>77,42%</t>
+          <t>77,6%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3649,12 +3649,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>588751</t>
+          <t>591317</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>643826</t>
+          <t>645574</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3664,12 +3664,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>68,9%</t>
+          <t>69,2%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>75,35%</t>
+          <t>75,55%</t>
         </is>
       </c>
     </row>
@@ -3809,12 +3809,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>27081</t>
+          <t>27100</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>49897</t>
+          <t>50435</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3824,12 +3824,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>14,54%</t>
+          <t>14,7%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3844,12 +3844,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>48175</t>
+          <t>48431</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>75977</t>
+          <t>78482</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
+          <t>16,53%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3879,12 +3879,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>80843</t>
+          <t>80162</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>118601</t>
+          <t>118170</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>14,45%</t>
         </is>
       </c>
     </row>
@@ -3922,12 +3922,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>10268</t>
+          <t>10187</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>27410</t>
+          <t>27778</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3937,12 +3937,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3957,12 +3957,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>35964</t>
+          <t>35010</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>63568</t>
+          <t>62239</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3972,12 +3972,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>13,11%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3992,12 +3992,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>49739</t>
+          <t>48896</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>82453</t>
+          <t>82009</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4007,12 +4007,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>10,03%</t>
         </is>
       </c>
     </row>
@@ -4035,12 +4035,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>27462</t>
+          <t>27043</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>51405</t>
+          <t>51444</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4050,12 +4050,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>14,98%</t>
+          <t>14,99%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>51500</t>
+          <t>52616</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>84420</t>
+          <t>83259</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4085,12 +4085,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>11,08%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>17,78%</t>
+          <t>17,53%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>84311</t>
+          <t>86167</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>124043</t>
+          <t>123460</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4120,12 +4120,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>10,53%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>15,09%</t>
         </is>
       </c>
     </row>
@@ -4148,12 +4148,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>233639</t>
+          <t>232745</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>265804</t>
+          <t>266394</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4163,12 +4163,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>68,1%</t>
+          <t>67,84%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>77,48%</t>
+          <t>77,65%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>276152</t>
+          <t>276159</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>320913</t>
+          <t>321248</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4203,7 +4203,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>67,58%</t>
+          <t>67,65%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>519502</t>
+          <t>523475</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>576897</t>
+          <t>575519</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4233,12 +4233,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>63,51%</t>
+          <t>64,0%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>70,53%</t>
+          <t>70,36%</t>
         </is>
       </c>
     </row>
@@ -4378,12 +4378,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>6505</t>
+          <t>5786</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>21511</t>
+          <t>20954</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4393,12 +4393,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>28,76%</t>
+          <t>28,01%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>6310</t>
+          <t>5609</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>19093</t>
+          <t>19159</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4428,12 +4428,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>18,23%</t>
+          <t>18,29%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>15199</t>
+          <t>15845</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>35806</t>
+          <t>34912</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4463,12 +4463,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,82%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>19,94%</t>
+          <t>19,44%</t>
         </is>
       </c>
     </row>
@@ -4491,12 +4491,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>902</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>8036</t>
+          <t>7352</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>4488</t>
+          <t>4443</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>17906</t>
+          <t>17238</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4541,12 +4541,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>17,09%</t>
+          <t>16,45%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>6571</t>
+          <t>6633</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>21488</t>
+          <t>21187</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -4576,12 +4576,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>11,97%</t>
+          <t>11,8%</t>
         </is>
       </c>
     </row>
@@ -4604,12 +4604,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1963</t>
+          <t>1936</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>14547</t>
+          <t>13637</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4619,12 +4619,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>19,45%</t>
+          <t>18,23%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4639,12 +4639,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4002</t>
+          <t>4065</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>16159</t>
+          <t>15423</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4654,12 +4654,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>15,42%</t>
+          <t>14,72%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4674,12 +4674,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>7273</t>
+          <t>7721</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>22898</t>
+          <t>23093</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4689,12 +4689,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,75%</t>
+          <t>12,86%</t>
         </is>
       </c>
     </row>
@@ -4717,12 +4717,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>43472</t>
+          <t>44732</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>61479</t>
+          <t>62481</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4732,12 +4732,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>58,12%</t>
+          <t>59,8%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>82,19%</t>
+          <t>83,53%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4752,12 +4752,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>65271</t>
+          <t>65164</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>84982</t>
+          <t>84938</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4767,12 +4767,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>62,3%</t>
+          <t>62,2%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>81,12%</t>
+          <t>81,08%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4787,12 +4787,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>113758</t>
+          <t>115898</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>140688</t>
+          <t>142042</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4802,12 +4802,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>63,35%</t>
+          <t>64,55%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>78,35%</t>
+          <t>79,11%</t>
         </is>
       </c>
     </row>
@@ -4947,12 +4947,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>75129</t>
+          <t>75536</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>112036</t>
+          <t>113549</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -4962,12 +4962,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>15,04%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -4982,12 +4982,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>96483</t>
+          <t>97008</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>138917</t>
+          <t>137722</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -4997,12 +4997,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>12,44%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5017,12 +5017,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>182171</t>
+          <t>183213</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>238829</t>
+          <t>240491</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5032,12 +5032,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>12,99%</t>
         </is>
       </c>
     </row>
@@ -5060,12 +5060,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>30684</t>
+          <t>29277</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>57485</t>
+          <t>56478</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5075,12 +5075,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5095,12 +5095,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>77325</t>
+          <t>78288</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>116455</t>
+          <t>114927</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5110,12 +5110,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5130,12 +5130,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>116479</t>
+          <t>116009</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>163003</t>
+          <t>162153</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>8,76%</t>
         </is>
       </c>
     </row>
@@ -5173,12 +5173,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>60400</t>
+          <t>61367</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>97174</t>
+          <t>96756</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>13,04%</t>
+          <t>12,99%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5208,12 +5208,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>111277</t>
+          <t>110828</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>155406</t>
+          <t>154172</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5223,12 +5223,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>10,01%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>14,04%</t>
+          <t>13,93%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5243,12 +5243,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>180926</t>
+          <t>180559</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>236973</t>
+          <t>237200</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5258,12 +5258,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>12,8%</t>
+          <t>12,81%</t>
         </is>
       </c>
     </row>
@@ -5286,12 +5286,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>505037</t>
+          <t>505105</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>554754</t>
+          <t>558682</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5301,12 +5301,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>67,79%</t>
+          <t>67,8%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>74,47%</t>
+          <t>75,0%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5321,12 +5321,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>725810</t>
+          <t>732130</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>790775</t>
+          <t>793274</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5336,12 +5336,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>65,56%</t>
+          <t>66,13%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>71,43%</t>
+          <t>71,66%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5356,12 +5356,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1255101</t>
+          <t>1249486</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1335009</t>
+          <t>1335686</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5371,12 +5371,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>67,77%</t>
+          <t>67,47%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>72,08%</t>
+          <t>72,12%</t>
         </is>
       </c>
     </row>
@@ -5747,12 +5747,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>21829</t>
+          <t>21462</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>41942</t>
+          <t>42040</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5762,12 +5762,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>16,99%</t>
+          <t>17,03%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5782,12 +5782,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>34300</t>
+          <t>33707</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>61378</t>
+          <t>59849</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5797,12 +5797,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>15,22%</t>
+          <t>14,84%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5817,12 +5817,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>59220</t>
+          <t>59305</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>94391</t>
+          <t>93806</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5832,12 +5832,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>14,52%</t>
+          <t>14,43%</t>
         </is>
       </c>
     </row>
@@ -5860,12 +5860,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7354</t>
+          <t>7791</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>22454</t>
+          <t>22111</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5875,12 +5875,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5895,12 +5895,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>20713</t>
+          <t>20798</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>43573</t>
+          <t>43103</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5910,12 +5910,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>10,69%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5930,12 +5930,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>32252</t>
+          <t>31376</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>59765</t>
+          <t>58888</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5945,12 +5945,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>9,06%</t>
         </is>
       </c>
     </row>
@@ -5973,12 +5973,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>17712</t>
+          <t>18084</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>37165</t>
+          <t>37502</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>15,05%</t>
+          <t>15,19%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6008,12 +6008,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>26009</t>
+          <t>26271</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>49935</t>
+          <t>49504</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6023,12 +6023,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>12,38%</t>
+          <t>12,28%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>50296</t>
+          <t>49391</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>79798</t>
+          <t>80777</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6058,12 +6058,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>12,42%</t>
         </is>
       </c>
     </row>
@@ -6086,12 +6086,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>161321</t>
+          <t>162506</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>189252</t>
+          <t>189166</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6101,12 +6101,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>65,33%</t>
+          <t>65,81%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>76,64%</t>
+          <t>76,61%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6121,12 +6121,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>270132</t>
+          <t>273768</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>308411</t>
+          <t>308842</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6136,12 +6136,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>66,99%</t>
+          <t>67,89%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>76,48%</t>
+          <t>76,59%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6156,12 +6156,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>444652</t>
+          <t>443225</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>489817</t>
+          <t>488112</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6171,12 +6171,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>68,39%</t>
+          <t>68,17%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>75,34%</t>
+          <t>75,07%</t>
         </is>
       </c>
     </row>
@@ -6316,12 +6316,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>31598</t>
+          <t>32726</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>58830</t>
+          <t>60744</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6331,12 +6331,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>13,09%</t>
+          <t>13,52%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6351,12 +6351,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>60955</t>
+          <t>61112</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>95186</t>
+          <t>95214</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6366,7 +6366,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>10,81%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -6386,12 +6386,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>100246</t>
+          <t>100782</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>141868</t>
+          <t>143894</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6401,12 +6401,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>13,98%</t>
+          <t>14,18%</t>
         </is>
       </c>
     </row>
@@ -6429,12 +6429,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>16162</t>
+          <t>16150</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>36862</t>
+          <t>35420</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6444,12 +6444,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>47840</t>
+          <t>47716</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>76884</t>
+          <t>78308</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6479,12 +6479,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>13,85%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6499,12 +6499,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>69073</t>
+          <t>69962</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>107366</t>
+          <t>104798</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6514,12 +6514,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>10,33%</t>
         </is>
       </c>
     </row>
@@ -6542,12 +6542,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>42768</t>
+          <t>42477</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>71756</t>
+          <t>70983</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6557,12 +6557,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>15,8%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>56676</t>
+          <t>57216</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>90127</t>
+          <t>90175</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6592,12 +6592,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>10,12%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>15,94%</t>
+          <t>15,95%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6612,12 +6612,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>107118</t>
+          <t>108540</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>150758</t>
+          <t>149116</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6627,12 +6627,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>14,7%</t>
         </is>
       </c>
     </row>
@@ -6655,12 +6655,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>305219</t>
+          <t>303934</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>344723</t>
+          <t>342143</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6670,12 +6670,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>67,93%</t>
+          <t>67,64%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>76,72%</t>
+          <t>76,14%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6690,12 +6690,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>330609</t>
+          <t>331557</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>377784</t>
+          <t>377668</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6705,12 +6705,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>58,48%</t>
+          <t>58,65%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>66,83%</t>
+          <t>66,81%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6725,12 +6725,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>650700</t>
+          <t>649072</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>711402</t>
+          <t>709592</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6740,12 +6740,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>64,13%</t>
+          <t>63,97%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>70,11%</t>
+          <t>69,94%</t>
         </is>
       </c>
     </row>
@@ -6885,12 +6885,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>7560</t>
+          <t>7283</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>23411</t>
+          <t>22274</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6900,12 +6900,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>20,4%</t>
+          <t>19,41%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6920,12 +6920,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>9386</t>
+          <t>9086</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>26258</t>
+          <t>27197</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6935,12 +6935,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>19,93%</t>
+          <t>20,65%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6955,12 +6955,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>20357</t>
+          <t>20780</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>42315</t>
+          <t>44578</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6970,12 +6970,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>17,17%</t>
+          <t>18,09%</t>
         </is>
       </c>
     </row>
@@ -6998,12 +6998,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5502</t>
+          <t>5367</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>19065</t>
+          <t>19368</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7013,12 +7013,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>16,62%</t>
+          <t>16,88%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -7033,12 +7033,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>8737</t>
+          <t>8355</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>23150</t>
+          <t>23323</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7048,12 +7048,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>17,57%</t>
+          <t>17,71%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -7068,12 +7068,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>17445</t>
+          <t>17820</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>37270</t>
+          <t>38098</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7083,12 +7083,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>15,12%</t>
+          <t>15,46%</t>
         </is>
       </c>
     </row>
@@ -7111,12 +7111,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>13725</t>
+          <t>13256</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>31297</t>
+          <t>32304</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7126,12 +7126,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>11,55%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>27,28%</t>
+          <t>28,15%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7146,12 +7146,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>8541</t>
+          <t>8221</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>22950</t>
+          <t>21492</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7161,12 +7161,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>17,42%</t>
+          <t>16,32%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7181,12 +7181,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>25851</t>
+          <t>24117</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>50076</t>
+          <t>48174</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7196,12 +7196,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>20,32%</t>
+          <t>19,55%</t>
         </is>
       </c>
     </row>
@@ -7224,12 +7224,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>56988</t>
+          <t>57480</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>78727</t>
+          <t>80161</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7239,12 +7239,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>49,67%</t>
+          <t>50,1%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>68,61%</t>
+          <t>69,86%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7259,12 +7259,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>73938</t>
+          <t>74188</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>96438</t>
+          <t>98137</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7274,12 +7274,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>56,13%</t>
+          <t>56,32%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>73,21%</t>
+          <t>74,5%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7294,12 +7294,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>139237</t>
+          <t>138442</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>170321</t>
+          <t>171167</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7309,12 +7309,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>56,49%</t>
+          <t>56,17%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>69,11%</t>
+          <t>69,45%</t>
         </is>
       </c>
     </row>
@@ -7454,12 +7454,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>72712</t>
+          <t>70666</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>109975</t>
+          <t>108092</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7469,12 +7469,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>13,56%</t>
+          <t>13,33%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7489,12 +7489,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>116166</t>
+          <t>115862</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>160977</t>
+          <t>165171</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7504,12 +7504,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>10,53%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>14,63%</t>
+          <t>15,01%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7524,12 +7524,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>198345</t>
+          <t>198114</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>256271</t>
+          <t>256499</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7539,12 +7539,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>13,42%</t>
         </is>
       </c>
     </row>
@@ -7567,12 +7567,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>35974</t>
+          <t>36145</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>64443</t>
+          <t>63862</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7582,12 +7582,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7602,12 +7602,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>87995</t>
+          <t>88337</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>128761</t>
+          <t>130418</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7617,12 +7617,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7637,12 +7637,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>130262</t>
+          <t>132725</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>182400</t>
+          <t>180849</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7652,12 +7652,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>9,46%</t>
         </is>
       </c>
     </row>
@@ -7680,12 +7680,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>86452</t>
+          <t>85225</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>126648</t>
+          <t>123036</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7695,12 +7695,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>15,62%</t>
+          <t>15,17%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7715,12 +7715,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>102421</t>
+          <t>102413</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>145921</t>
+          <t>142897</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7735,7 +7735,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>13,26%</t>
+          <t>12,99%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7750,12 +7750,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>198252</t>
+          <t>199882</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>259132</t>
+          <t>255581</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7765,12 +7765,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>10,46%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>13,56%</t>
+          <t>13,37%</t>
         </is>
       </c>
     </row>
@@ -7793,12 +7793,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>541649</t>
+          <t>543257</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>593956</t>
+          <t>596164</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7808,12 +7808,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>66,79%</t>
+          <t>66,99%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>73,24%</t>
+          <t>73,51%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7828,12 +7828,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>697678</t>
+          <t>700705</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>761883</t>
+          <t>765277</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7843,12 +7843,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>63,41%</t>
+          <t>63,68%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>69,24%</t>
+          <t>69,55%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7863,12 +7863,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1258184</t>
+          <t>1258380</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1343151</t>
+          <t>1345545</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7878,12 +7878,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>65,83%</t>
+          <t>65,84%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>70,27%</t>
+          <t>70,4%</t>
         </is>
       </c>
     </row>
@@ -8249,32 +8249,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>22353</t>
+          <t>24692</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>15650</t>
+          <t>16944</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>31106</t>
+          <t>33538</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>18,03%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>12,37%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>24,11%</t>
+          <t>24,49%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8284,67 +8284,67 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>43105</t>
+          <t>48781</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>33795</t>
+          <t>39455</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>52602</t>
+          <t>59280</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
+          <t>20,61%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>16,67%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>25,04%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>73473</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>61021</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>88026</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
           <t>19,66%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>15,41%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>23,99%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>108</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>65458</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>53744</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>77995</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>18,8%</t>
-        </is>
-      </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>16,33%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>22,4%</t>
+          <t>23,55%</t>
         </is>
       </c>
     </row>
@@ -8362,32 +8362,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>42174</t>
+          <t>44548</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>32535</t>
+          <t>35281</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>52797</t>
+          <t>56363</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>32,69%</t>
+          <t>32,53%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>25,22%</t>
+          <t>25,76%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>40,93%</t>
+          <t>41,15%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8397,32 +8397,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>64766</t>
+          <t>65990</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>54658</t>
+          <t>54866</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>80000</t>
+          <t>76832</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>29,54%</t>
+          <t>27,87%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>24,93%</t>
+          <t>23,18%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>36,48%</t>
+          <t>32,45%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8432,32 +8432,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>106940</t>
+          <t>110538</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>93425</t>
+          <t>96726</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>123457</t>
+          <t>125819</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>30,71%</t>
+          <t>29,58%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>26,83%</t>
+          <t>25,88%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>35,45%</t>
+          <t>33,67%</t>
         </is>
       </c>
     </row>
@@ -8475,32 +8475,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>22559</t>
+          <t>23125</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>16251</t>
+          <t>15772</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>31595</t>
+          <t>32740</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>17,49%</t>
+          <t>16,88%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>11,52%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>24,49%</t>
+          <t>23,9%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8510,32 +8510,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>46739</t>
+          <t>54246</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>37040</t>
+          <t>43865</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>55333</t>
+          <t>64491</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>21,32%</t>
+          <t>22,91%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>16,89%</t>
+          <t>18,53%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>25,23%</t>
+          <t>27,24%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8545,32 +8545,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>69298</t>
+          <t>77372</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>57745</t>
+          <t>65045</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>81840</t>
+          <t>89593</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>19,9%</t>
+          <t>20,7%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>16,58%</t>
+          <t>17,41%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>23,5%</t>
+          <t>23,97%</t>
         </is>
       </c>
     </row>
@@ -8588,32 +8588,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>41910</t>
+          <t>44598</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>32857</t>
+          <t>35466</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>51192</t>
+          <t>55338</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>32,49%</t>
+          <t>32,56%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>25,47%</t>
+          <t>25,89%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>39,68%</t>
+          <t>40,4%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8623,32 +8623,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>64663</t>
+          <t>67726</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>54278</t>
+          <t>56838</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>75301</t>
+          <t>79236</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>29,49%</t>
+          <t>28,61%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>24,75%</t>
+          <t>24,01%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>34,34%</t>
+          <t>33,47%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8658,32 +8658,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>106572</t>
+          <t>112324</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>93480</t>
+          <t>98748</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>122026</t>
+          <t>128411</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>30,6%</t>
+          <t>30,06%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>26,84%</t>
+          <t>26,42%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>35,04%</t>
+          <t>34,36%</t>
         </is>
       </c>
     </row>
@@ -8701,17 +8701,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>128996</t>
+          <t>136963</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>128996</t>
+          <t>136963</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>128996</t>
+          <t>136963</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8736,17 +8736,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>219272</t>
+          <t>236743</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>219272</t>
+          <t>236743</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>219272</t>
+          <t>236743</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8771,17 +8771,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>348268</t>
+          <t>373706</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>348268</t>
+          <t>373706</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>348268</t>
+          <t>373706</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8818,32 +8818,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>58310</t>
+          <t>63023</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>45438</t>
+          <t>48656</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>72811</t>
+          <t>77497</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>16,54%</t>
+          <t>16,66%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>12,86%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>20,65%</t>
+          <t>20,49%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8853,32 +8853,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>89429</t>
+          <t>100243</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>53971</t>
+          <t>84412</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>112293</t>
+          <t>117802</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>18,54%</t>
+          <t>21,45%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>18,07%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>23,29%</t>
+          <t>25,21%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8888,32 +8888,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>147739</t>
+          <t>163267</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>109826</t>
+          <t>142324</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>172104</t>
+          <t>186660</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>17,7%</t>
+          <t>19,31%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>16,83%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>20,61%</t>
+          <t>22,08%</t>
         </is>
       </c>
     </row>
@@ -8931,32 +8931,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>98324</t>
+          <t>107061</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>80823</t>
+          <t>88467</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>115090</t>
+          <t>125292</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>27,88%</t>
+          <t>28,31%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>22,92%</t>
+          <t>23,39%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>32,64%</t>
+          <t>33,13%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8966,32 +8966,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>127458</t>
+          <t>146735</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>77916</t>
+          <t>128406</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>156805</t>
+          <t>165087</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>26,43%</t>
+          <t>31,41%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>27,48%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>32,51%</t>
+          <t>35,33%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9001,32 +9001,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>225783</t>
+          <t>253797</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>175433</t>
+          <t>228607</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>258929</t>
+          <t>278572</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
+          <t>30,02%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
           <t>27,04%</t>
         </is>
       </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>21,01%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>31,01%</t>
+          <t>32,95%</t>
         </is>
       </c>
     </row>
@@ -9044,32 +9044,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>66507</t>
+          <t>70876</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>51885</t>
+          <t>55976</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>84517</t>
+          <t>88739</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>18,86%</t>
+          <t>18,74%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>14,71%</t>
+          <t>14,8%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>23,97%</t>
+          <t>23,46%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9079,32 +9079,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>133714</t>
+          <t>72559</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>70726</t>
+          <t>60246</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>263283</t>
+          <t>87440</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>27,73%</t>
+          <t>15,53%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>12,89%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>54,59%</t>
+          <t>18,71%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9114,32 +9114,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>200221</t>
+          <t>143435</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>134286</t>
+          <t>122660</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>341891</t>
+          <t>166646</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>23,98%</t>
+          <t>16,97%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>16,08%</t>
+          <t>14,51%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>40,95%</t>
+          <t>19,71%</t>
         </is>
       </c>
     </row>
@@ -9157,22 +9157,22 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>129488</t>
+          <t>137255</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>110776</t>
+          <t>118800</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>151817</t>
+          <t>161007</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>36,72%</t>
+          <t>36,29%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -9182,7 +9182,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>43,05%</t>
+          <t>42,57%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -9192,32 +9192,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>131653</t>
+          <t>147693</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>84361</t>
+          <t>128018</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>160297</t>
+          <t>168651</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>27,3%</t>
+          <t>31,61%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17,49%</t>
+          <t>27,4%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>33,24%</t>
+          <t>36,1%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -9227,32 +9227,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>261141</t>
+          <t>284948</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>192310</t>
+          <t>257381</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>296594</t>
+          <t>313049</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>31,28%</t>
+          <t>33,7%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>23,03%</t>
+          <t>30,44%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>35,53%</t>
+          <t>37,03%</t>
         </is>
       </c>
     </row>
@@ -9270,17 +9270,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>352630</t>
+          <t>378216</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>352630</t>
+          <t>378216</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>352630</t>
+          <t>378216</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9305,17 +9305,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>482254</t>
+          <t>467230</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>482254</t>
+          <t>467230</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>482254</t>
+          <t>467230</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9340,17 +9340,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>834884</t>
+          <t>845446</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>834884</t>
+          <t>845446</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>834884</t>
+          <t>845446</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9387,32 +9387,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>29287</t>
+          <t>32383</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>20610</t>
+          <t>23122</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>39757</t>
+          <t>43323</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>23,61%</t>
+          <t>23,87%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>16,62%</t>
+          <t>17,04%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>32,05%</t>
+          <t>31,94%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9422,32 +9422,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>23921</t>
+          <t>28534</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>17184</t>
+          <t>20669</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>32092</t>
+          <t>37617</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>16,17%</t>
+          <t>17,09%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>12,38%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>21,7%</t>
+          <t>22,53%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9457,32 +9457,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>53208</t>
+          <t>60917</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>40794</t>
+          <t>47245</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>66635</t>
+          <t>75506</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>19,56%</t>
+          <t>20,13%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>15,61%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>24,5%</t>
+          <t>24,95%</t>
         </is>
       </c>
     </row>
@@ -9500,32 +9500,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>33899</t>
+          <t>36759</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>24410</t>
+          <t>26195</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>44178</t>
+          <t>48220</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>27,33%</t>
+          <t>27,1%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>19,68%</t>
+          <t>19,31%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>35,61%</t>
+          <t>35,55%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -9535,32 +9535,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>48371</t>
+          <t>53723</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>38814</t>
+          <t>43118</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>57575</t>
+          <t>64436</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>32,7%</t>
+          <t>32,18%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>26,24%</t>
+          <t>25,83%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>38,92%</t>
+          <t>38,59%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -9570,32 +9570,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>82270</t>
+          <t>90482</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>69294</t>
+          <t>74815</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>98532</t>
+          <t>106034</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>30,25%</t>
+          <t>29,9%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>25,48%</t>
+          <t>24,72%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>36,23%</t>
+          <t>35,04%</t>
         </is>
       </c>
     </row>
@@ -9613,32 +9613,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>21584</t>
+          <t>21692</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>14066</t>
+          <t>13694</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>32616</t>
+          <t>32723</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>15,99%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>10,09%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>26,29%</t>
+          <t>24,12%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9648,32 +9648,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>22326</t>
+          <t>25981</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>16024</t>
+          <t>18048</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>31728</t>
+          <t>35439</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>15,09%</t>
+          <t>15,56%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>10,81%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>21,45%</t>
+          <t>21,23%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9683,32 +9683,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>43909</t>
+          <t>47673</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>32496</t>
+          <t>36817</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>55906</t>
+          <t>61424</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>16,15%</t>
+          <t>15,75%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>12,17%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>20,56%</t>
+          <t>20,3%</t>
         </is>
       </c>
     </row>
@@ -9726,32 +9726,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>39274</t>
+          <t>44824</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>29655</t>
+          <t>34153</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>51854</t>
+          <t>59007</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>31,66%</t>
+          <t>33,04%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>23,91%</t>
+          <t>25,18%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>41,8%</t>
+          <t>43,5%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9761,32 +9761,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>53302</t>
+          <t>58721</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>43664</t>
+          <t>47729</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>64370</t>
+          <t>69846</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>36,03%</t>
+          <t>35,17%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>29,52%</t>
+          <t>28,59%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>43,52%</t>
+          <t>41,83%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9796,32 +9796,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>92576</t>
+          <t>103545</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>78279</t>
+          <t>86810</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>108881</t>
+          <t>120827</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>34,04%</t>
+          <t>34,22%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>28,78%</t>
+          <t>28,69%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>40,04%</t>
+          <t>39,93%</t>
         </is>
       </c>
     </row>
@@ -9839,17 +9839,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>124044</t>
+          <t>135658</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>124044</t>
+          <t>135658</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>124044</t>
+          <t>135658</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9874,17 +9874,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>147920</t>
+          <t>166960</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>147920</t>
+          <t>166960</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>147920</t>
+          <t>166960</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9909,17 +9909,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>271963</t>
+          <t>302618</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>271963</t>
+          <t>302618</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>271963</t>
+          <t>302618</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9956,32 +9956,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>109950</t>
+          <t>120098</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>90994</t>
+          <t>101987</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>130505</t>
+          <t>140897</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>18,15%</t>
+          <t>18,45%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>15,02%</t>
+          <t>15,67%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>21,55%</t>
+          <t>21,65%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9991,32 +9991,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>156456</t>
+          <t>177559</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>116052</t>
+          <t>157889</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>180560</t>
+          <t>198228</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>18,42%</t>
+          <t>20,39%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>18,13%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>21,26%</t>
+          <t>22,76%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10026,32 +10026,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>266406</t>
+          <t>297657</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>225253</t>
+          <t>269367</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>298623</t>
+          <t>328039</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>18,31%</t>
+          <t>19,56%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>15,48%</t>
+          <t>17,7%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>20,52%</t>
+          <t>21,56%</t>
         </is>
       </c>
     </row>
@@ -10069,32 +10069,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>174398</t>
+          <t>188368</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>153240</t>
+          <t>166318</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>196919</t>
+          <t>212312</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>28,79%</t>
+          <t>28,94%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>25,3%</t>
+          <t>25,55%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>32,51%</t>
+          <t>32,62%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10104,32 +10104,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>240594</t>
+          <t>266449</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>176315</t>
+          <t>240391</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>273411</t>
+          <t>288828</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>28,32%</t>
+          <t>30,59%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>20,76%</t>
+          <t>27,6%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>32,19%</t>
+          <t>33,16%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10139,32 +10139,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>414993</t>
+          <t>454817</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>355743</t>
+          <t>422602</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>455221</t>
+          <t>488137</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>28,52%</t>
+          <t>29,89%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>24,45%</t>
+          <t>27,77%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>31,28%</t>
+          <t>32,08%</t>
         </is>
       </c>
     </row>
@@ -10182,32 +10182,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>110650</t>
+          <t>115693</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>93618</t>
+          <t>94520</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>132532</t>
+          <t>135656</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>18,27%</t>
+          <t>17,78%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>14,52%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>21,88%</t>
+          <t>20,84%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -10217,32 +10217,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>202778</t>
+          <t>152786</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>139544</t>
+          <t>134428</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>395670</t>
+          <t>173312</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>23,87%</t>
+          <t>17,54%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>16,43%</t>
+          <t>15,43%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>46,58%</t>
+          <t>19,9%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -10252,32 +10252,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>313428</t>
+          <t>268480</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>245280</t>
+          <t>241500</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>494161</t>
+          <t>299417</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>21,54%</t>
+          <t>17,64%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>16,86%</t>
+          <t>15,87%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>33,96%</t>
+          <t>19,68%</t>
         </is>
       </c>
     </row>
@@ -10295,32 +10295,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>210671</t>
+          <t>226677</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>186270</t>
+          <t>204148</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>235411</t>
+          <t>255214</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>34,78%</t>
+          <t>34,83%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>30,75%</t>
+          <t>31,37%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>38,87%</t>
+          <t>39,21%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10330,32 +10330,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>249617</t>
+          <t>274140</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>178253</t>
+          <t>248756</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>280993</t>
+          <t>300637</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>29,39%</t>
+          <t>31,48%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>20,98%</t>
+          <t>28,56%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>33,08%</t>
+          <t>34,52%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10365,32 +10365,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>460289</t>
+          <t>500817</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>387525</t>
+          <t>464676</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>500011</t>
+          <t>535005</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>31,63%</t>
+          <t>32,91%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>26,63%</t>
+          <t>30,54%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>34,36%</t>
+          <t>35,16%</t>
         </is>
       </c>
     </row>
@@ -10408,17 +10408,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>605669</t>
+          <t>650836</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>605669</t>
+          <t>650836</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>605669</t>
+          <t>650836</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10443,17 +10443,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>849446</t>
+          <t>870934</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>849446</t>
+          <t>870934</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>849446</t>
+          <t>870934</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10478,17 +10478,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1455115</t>
+          <t>1521770</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1455115</t>
+          <t>1521770</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1455115</t>
+          <t>1521770</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
